--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-230.9%</t>
+          <t>-231.0%</t>
         </is>
       </c>
     </row>
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.634532625428458</v>
+        <v>-4.634326740443646</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7550188594755285</v>
+        <v>0.7551012134694537</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7638410771575341</v>
+        <v>-0.7643277082586507</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.150883687666139</v>
+        <v>2.150591709005469</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.8%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.0%</t>
+          <t>444.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.0%</t>
+          <t>-614.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.2%</t>
+          <t>-42.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-300.7%</t>
+          <t>-296.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-300.4%</t>
+          <t>-297.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-231.0%</t>
+          <t>-229.0%</t>
         </is>
       </c>
     </row>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.704283534069131</v>
+        <v>3.704283534069133</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.634326740443646</v>
+        <v>-4.528641496063044</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7551012134694537</v>
+        <v>0.7973753112216941</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7643277082586507</v>
+        <v>-0.7312285388688564</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.150591709005469</v>
+        <v>2.170451210639345</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-81.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.2%</t>
+          <t>439.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.4%</t>
+          <t>-638.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-43.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-113.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-296.5%</t>
+          <t>-306.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-297.1%</t>
+          <t>-299.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-229.0%</t>
+          <t>-230.4%</t>
         </is>
       </c>
     </row>
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.95311252485442</v>
+        <v>-12.10068032251469</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.60575080046231</v>
+        <v>-1.664777919526418</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.323727438065055</v>
+        <v>-3.323096465367529</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.181614170954172</v>
+        <v>1.181992754572687</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.66683771253172</v>
+        <v>-11.81440551019199</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.490101730977174</v>
+        <v>-1.549128850041281</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.323727438065055</v>
+        <v>-3.323096465367529</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.182753315510231</v>
+        <v>1.183131899128746</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.71973300057601</v>
+        <v>-11.86730079823628</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.50862607203278</v>
+        <v>-1.567653191096888</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.318772091976609</v>
+        <v>-3.318141119279083</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.188360297325406</v>
+        <v>1.188738880943922</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.43582426964726</v>
+        <v>-11.58339206730753</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.389328875422644</v>
+        <v>-1.448355994486752</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.318772091976609</v>
+        <v>-3.318141119279083</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.194094001564043</v>
+        <v>1.194472585182558</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.32040334550917</v>
+        <v>-11.46797114316943</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.352897768161271</v>
+        <v>-1.411924887225378</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.202720195140988</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.253609293653035</v>
+        <v>1.25398787727155</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.0565664783051</v>
+        <v>-11.20413427596536</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.257246502592551</v>
+        <v>-1.316273621656658</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.202720195140988</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.243725812340127</v>
+        <v>1.244104395958643</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.7893246774367</v>
+        <v>-10.93689247509697</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.152184342744565</v>
+        <v>-1.211211461808673</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.202720195140988</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.241891251840753</v>
+        <v>1.242269835459269</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.66601874895848</v>
+        <v>-10.81358654661875</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.103162286326738</v>
+        <v>-1.162189405390846</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.11393349671095</v>
+        <v>-3.113302524013425</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.29524153954383</v>
+        <v>1.295620123162346</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.64206520798252</v>
+        <v>-10.78963300564279</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.092912363790862</v>
+        <v>-1.151939482854969</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.089979955734993</v>
+        <v>-3.089348983037468</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.310282170274899</v>
+        <v>1.310660753893414</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.37800526965972</v>
+        <v>-10.52557306731999</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.000548704623495</v>
+        <v>-1.059575823687602</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.825920017412197</v>
+        <v>-2.825289044714671</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.455457817106824</v>
+        <v>1.455836400725339</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.670925646154886</v>
+        <v>-9.818493443815155</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7205038888818609</v>
+        <v>-0.7795310079459687</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.825920017412197</v>
+        <v>-2.825289044714671</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.452670783446523</v>
+        <v>1.453049367065039</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.630741347788696</v>
+        <v>-9.778309145448965</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7040865456475434</v>
+        <v>-0.7631136647116512</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.785735719046006</v>
+        <v>-2.78510474634848</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.477124986354079</v>
+        <v>1.477503569972594</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.550671552250892</v>
+        <v>-9.698239349911161</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6726918062116649</v>
+        <v>-0.7317189252757723</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.705665923508202</v>
+        <v>-2.705034950810676</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.524533684897519</v>
+        <v>1.524912268516034</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.317190330021294</v>
+        <v>-9.464758127681563</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5713748884819734</v>
+        <v>-0.6304020075460808</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.472184701278603</v>
+        <v>-2.471553728581078</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.67254684707313</v>
+        <v>1.672925430691645</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.13748179987742</v>
+        <v>-9.285049597537689</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.502383686737383</v>
+        <v>-0.5614108058014908</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.415013197115907</v>
+        <v>-2.414382224418382</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.703957539257788</v>
+        <v>1.704336122876304</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.005206326246533</v>
+        <v>-9.152774123906802</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.454106010538001</v>
+        <v>-0.5131331296021089</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.282737723485021</v>
+        <v>-2.282106750787495</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.778690310183347</v>
+        <v>1.779068893801863</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.81460665157338</v>
+        <v>-8.962174449233649</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3750510799811031</v>
+        <v>-0.4340781990452105</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.092138048811868</v>
+        <v>-2.091507076114343</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.895865175674876</v>
+        <v>1.896243759293391</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.565606852889799</v>
+        <v>-8.713174650550068</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2625448192840119</v>
+        <v>-0.3215719383481193</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.092138048811868</v>
+        <v>-2.091507076114343</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.908771516898534</v>
+        <v>1.909150100517049</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.671196842662903</v>
+        <v>-8.818764640323172</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4327567447924725</v>
+        <v>-0.4917838638565799</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.197728038584973</v>
+        <v>-2.197097065887447</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.717441593435453</v>
+        <v>1.717820177053968</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.6899317447815</v>
+        <v>-8.837499542441769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3917063637628249</v>
+        <v>-0.4507334828269323</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.197728038584973</v>
+        <v>-2.197097065887447</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.765985935312539</v>
+        <v>1.766364518931055</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.541991703373901</v>
+        <v>-8.68955950103417</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4524092698879527</v>
+        <v>-0.5114363889520601</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.177407122676415</v>
+        <v>-2.17677614997889</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.658299562169506</v>
+        <v>1.658678145788022</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.517763066984928</v>
+        <v>-8.665330864645197</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4514318015858416</v>
+        <v>-0.5104589206499495</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.152547513589917</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.664122757749412</v>
+        <v>1.664501341367927</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.474214660214237</v>
+        <v>-8.621782457874506</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4409730509726586</v>
+        <v>-0.500000170036766</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.152547513589917</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.657162145654318</v>
+        <v>1.657540729272833</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.232066266760379</v>
+        <v>-8.379634064420648</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3296513392099722</v>
+        <v>-0.3886784582740797</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.152547513589917</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.671624500035461</v>
+        <v>1.672003083653977</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.168836894992031</v>
+        <v>-8.3164046926523</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3098274700434382</v>
+        <v>-0.3688545891075456</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.152547513589917</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.666156620494657</v>
+        <v>1.666535204113172</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.045545760174901</v>
+        <v>-8.19311355783517</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2630129221060091</v>
+        <v>-0.322040041170117</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.029887351470312</v>
+        <v>-2.029256378772787</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.737629395395512</v>
+        <v>1.738007979014027</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.024396561271459</v>
+        <v>-8.171964358931728</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2468522643073072</v>
+        <v>-0.3058793833714146</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.008738152566869</v>
+        <v>-2.008107179869344</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.758019892974903</v>
+        <v>1.758398476593418</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.780631119288015</v>
+        <v>-7.928198916948284</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1535653791668787</v>
+        <v>-0.2125924982309861</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.008738152566869</v>
+        <v>-2.008107179869344</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.753800601321953</v>
+        <v>1.754179184940469</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.516603052094755</v>
+        <v>-7.664170849755024</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.04582983836955901</v>
+        <v>-0.1048569574336664</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.80624178105339</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.877044154531541</v>
+        <v>1.877422738150057</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.26675265814568</v>
+        <v>-7.414320455805949</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.04685239419377307</v>
+        <v>-0.01217472487033433</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.80624178105339</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.869786229515244</v>
+        <v>1.870164813133759</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.090860565678248</v>
+        <v>-7.238428363338517</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1208083547013947</v>
+        <v>0.06178123563728732</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.80624178105339</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.873385353035892</v>
+        <v>1.873763936654408</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.017380656826234</v>
+        <v>-7.164948454486503</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1635278242967542</v>
+        <v>0.1045007052326468</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.733392844898901</v>
+        <v>-1.732761872201376</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.930800804401655</v>
+        <v>1.93117938802017</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.792347657157411</v>
+        <v>-6.93991545481768</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2525615017805807</v>
+        <v>0.1935343827164728</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.508359845230078</v>
+        <v>-1.507728872532553</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.064841081819246</v>
+        <v>2.065219665437761</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.577713279521004</v>
+        <v>-6.725281077181273</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3431100538894607</v>
+        <v>0.2840829348253529</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.293725467593672</v>
+        <v>-1.293094494896146</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.198316509455407</v>
+        <v>2.198695093073922</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.311112922546652</v>
+        <v>-6.458680720206921</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4309444554629969</v>
+        <v>0.3719173363988895</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.293725467593672</v>
+        <v>-1.293094494896146</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.179510768239203</v>
+        <v>2.179889351857717</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712295</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.070682425741792</v>
+        <v>-6.218250223402061</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5288597308098182</v>
+        <v>0.4698326117457108</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.053294970788811</v>
+        <v>-1.052663998091286</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.325512142946996</v>
+        <v>2.325890726565511</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.827891618092346</v>
+        <v>-5.975459415752615</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6299053677044166</v>
+        <v>0.5708782486403092</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.053294970788811</v>
+        <v>-1.052663998091286</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.329441456781816</v>
+        <v>2.329820040400331</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349968</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.711951768467161</v>
+        <v>-5.85951956612743</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6769598914718311</v>
+        <v>0.6179327724077233</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9764732397726874</v>
+        <v>-0.9758422670751621</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.376213079308831</v>
+        <v>2.376591662927346</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.469296180043997</v>
+        <v>-5.616863977704266</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7710201980610898</v>
+        <v>0.7119930789969824</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9764732397726874</v>
+        <v>-0.9758422670751621</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.373211150528824</v>
+        <v>2.373589734147339</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.249275382006987</v>
+        <v>-5.396843179667256</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8606075542865081</v>
+        <v>0.8015804352224007</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8352533947047072</v>
+        <v>-0.8346224220071818</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.459522094580226</v>
+        <v>2.459900678198741</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.050026752102178</v>
+        <v>-5.197594549762447</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9562011890502551</v>
+        <v>0.8971740699861477</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8352533947047072</v>
+        <v>-0.8346224220071818</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.475416277382049</v>
+        <v>2.475794861000565</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.890511648582808</v>
+        <v>-5.038079446243077</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.021153074898305</v>
+        <v>0.9621259558341975</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6757382911853372</v>
+        <v>-0.6751073184878119</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.572271183933974</v>
+        <v>2.572649767552488</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.74583950348307</v>
+        <v>-4.893407301143339</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.08911003549964</v>
+        <v>1.030082916435532</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5310661460855999</v>
+        <v>-0.5304351733880746</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.669162573555256</v>
+        <v>2.669541157173771</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.805714330840763</v>
+        <v>-4.953282128501032</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.051197595957989</v>
+        <v>0.992170476893881</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.590940973443292</v>
+        <v>-0.5903100007457667</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.619275168542066</v>
+        <v>2.619653752160581</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.718914833061755</v>
+        <v>-4.866482630722023</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.108317888392158</v>
+        <v>1.049290769328051</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.590940973443292</v>
+        <v>-0.5903100007457667</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.641675661864632</v>
+        <v>2.642054245483147</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.721384539523561</v>
+        <v>-4.868952337183829</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.107402407180848</v>
+        <v>1.04837528811674</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5934106799050982</v>
+        <v>-0.5927797072075729</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.640266239360961</v>
+        <v>2.640644822979476</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.789754725847571</v>
+        <v>-4.93732252350784</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.091061255125946</v>
+        <v>1.032034136061838</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.5835040081713579</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.656838581257392</v>
+        <v>2.657217164875907</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.668338296221094</v>
+        <v>-4.815906093881363</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.130064535608428</v>
+        <v>1.07103741654432</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.5835040081713579</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.647275289889283</v>
+        <v>2.647653873507798</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.6993314555498</v>
+        <v>-4.846899253210069</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9423768369173324</v>
+        <v>0.8833497178532248</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.5835040081713579</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.47198485492967</v>
+        <v>2.472363438548185</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675903</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.52385719575733</v>
+        <v>-4.671424993417599</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.017133772826108</v>
+        <v>0.9581066537620004</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.5835040081713579</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.476552086921457</v>
+        <v>2.476930670539973</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.634793448398579</v>
+        <v>-4.782361246058848</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9727707456564061</v>
+        <v>0.9137436265922985</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.5835040081713579</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.476563560808255</v>
+        <v>2.47694214442677</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581296</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.837820025941812</v>
+        <v>-4.985387823602081</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8946914998590183</v>
+        <v>0.8356643807949107</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7871615584121167</v>
+        <v>-0.7865305857145913</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.35787899950222</v>
+        <v>2.358257583120736</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734165</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.679894427006519</v>
+        <v>-4.827462224666788</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9680341258652678</v>
+        <v>0.9090070068011602</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7871615584121167</v>
+        <v>-0.7865305857145913</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.368051385934353</v>
+        <v>2.368429969552868</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212301</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.828215680817648</v>
+        <v>-4.975783478477917</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9036518949146766</v>
+        <v>0.8446247758505692</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7871615584121167</v>
+        <v>-0.7865305857145913</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.362997656508213</v>
+        <v>2.363376240126728</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786049</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.829398765468708</v>
+        <v>-4.976966563128977</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.894954436498778</v>
+        <v>0.8359273174346704</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7928046068786282</v>
+        <v>-0.7921736341811029</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.351387602872832</v>
+        <v>2.351766186491347</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273194</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.706271058474625</v>
+        <v>-4.853838856134894</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9447573923295127</v>
+        <v>0.8857302732654051</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7928046068786282</v>
+        <v>-0.7921736341811029</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.351939475905934</v>
+        <v>2.352318059524449</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279503</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.613460577023766</v>
+        <v>-4.761028374684035</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9111542768012222</v>
+        <v>0.8521271577371148</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6999941254277688</v>
+        <v>-0.6993631527302435</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.336898456667815</v>
+        <v>2.33727704028633</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030431</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.564897524802736</v>
+        <v>-4.712465322463005</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9324529736142351</v>
+        <v>0.8734258545501274</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6514310732067387</v>
+        <v>-0.6508001005092133</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.367909763925033</v>
+        <v>2.368288347543549</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942743</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.452226306566486</v>
+        <v>-4.599794104226754</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.972597169420458</v>
+        <v>0.9135700503563506</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5387598549704884</v>
+        <v>-0.5381288822729631</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.430588203378507</v>
+        <v>2.430966786997022</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268541</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.339849305383813</v>
+        <v>-4.487417103044081</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.023039265724194</v>
+        <v>0.9640121466600871</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5387598549704884</v>
+        <v>-0.5381288822729631</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.436079499209174</v>
+        <v>2.436458082827689</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968866</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.538083874270543</v>
+        <v>-4.685651671930812</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9552426399380414</v>
+        <v>0.8962155208739337</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.736994423857219</v>
+        <v>-0.7363634511596937</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.328635959645675</v>
+        <v>2.32901454326419</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.704283534069133</v>
+        <v>3.351838675471003</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.528641496063044</v>
+        <v>-4.768652952956091</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7973753112216941</v>
+        <v>0.7013707284644755</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7312285388688564</v>
+        <v>-0.7549343356868674</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.170451210639345</v>
+        <v>2.156227732548539</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.4%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.4%</t>
+          <t>444.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-638.4%</t>
+          <t>-614.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.2%</t>
+          <t>-42.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-113.5%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-296.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-299.5%</t>
+          <t>-297.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-230.4%</t>
+          <t>-176.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1951"/>
+  <dimension ref="A1:G1952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.49684832919989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.10068032251469</v>
+        <v>-11.95311252485442</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.664777919526418</v>
+        <v>-1.60575080046231</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.323096465367529</v>
+        <v>-3.323727438065055</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.181992754572687</v>
+        <v>1.181614170954172</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.81440551019199</v>
+        <v>-11.66683771253172</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.549128850041281</v>
+        <v>-1.490101730977174</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.323096465367529</v>
+        <v>-3.323727438065055</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.183131899128746</v>
+        <v>1.182753315510231</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.86730079823628</v>
+        <v>-11.71973300057601</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.567653191096888</v>
+        <v>-1.50862607203278</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.318141119279083</v>
+        <v>-3.318772091976609</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.188738880943922</v>
+        <v>1.188360297325406</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.58339206730753</v>
+        <v>-11.43582426964726</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.448355994486752</v>
+        <v>-1.389328875422644</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.318141119279083</v>
+        <v>-3.318772091976609</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.194472585182558</v>
+        <v>1.194094001564043</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.46797114316943</v>
+        <v>-11.32040334550917</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.411924887225378</v>
+        <v>-1.352897768161271</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.202720195140988</v>
+        <v>-3.203351167838513</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.25398787727155</v>
+        <v>1.253609293653035</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.20413427596536</v>
+        <v>-11.0565664783051</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.316273621656658</v>
+        <v>-1.257246502592551</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.202720195140988</v>
+        <v>-3.203351167838513</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.244104395958643</v>
+        <v>1.243725812340127</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.93689247509697</v>
+        <v>-10.7893246774367</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.211211461808673</v>
+        <v>-1.152184342744565</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.202720195140988</v>
+        <v>-3.203351167838513</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.242269835459269</v>
+        <v>1.241891251840753</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.81358654661875</v>
+        <v>-10.66601874895848</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.162189405390846</v>
+        <v>-1.103162286326738</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.113302524013425</v>
+        <v>-3.11393349671095</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.295620123162346</v>
+        <v>1.29524153954383</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.78963300564279</v>
+        <v>-10.64206520798252</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.151939482854969</v>
+        <v>-1.092912363790862</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.089348983037468</v>
+        <v>-3.089979955734993</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.310660753893414</v>
+        <v>1.310282170274899</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.52557306731999</v>
+        <v>-10.37800526965972</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.059575823687602</v>
+        <v>-1.000548704623495</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.825289044714671</v>
+        <v>-2.825920017412197</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.455836400725339</v>
+        <v>1.455457817106824</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.818493443815155</v>
+        <v>-9.670925646154886</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7795310079459687</v>
+        <v>-0.7205038888818609</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.825289044714671</v>
+        <v>-2.825920017412197</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.453049367065039</v>
+        <v>1.452670783446523</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.778309145448965</v>
+        <v>-9.630741347788696</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7631136647116512</v>
+        <v>-0.7040865456475434</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.78510474634848</v>
+        <v>-2.785735719046006</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.477503569972594</v>
+        <v>1.477124986354079</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.698239349911161</v>
+        <v>-9.550671552250892</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7317189252757723</v>
+        <v>-0.6726918062116649</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.705034950810676</v>
+        <v>-2.705665923508202</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.524912268516034</v>
+        <v>1.524533684897519</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.464758127681563</v>
+        <v>-9.317190330021294</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6304020075460808</v>
+        <v>-0.5713748884819734</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.471553728581078</v>
+        <v>-2.472184701278603</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.672925430691645</v>
+        <v>1.67254684707313</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.285049597537689</v>
+        <v>-9.13748179987742</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5614108058014908</v>
+        <v>-0.502383686737383</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.414382224418382</v>
+        <v>-2.415013197115907</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.704336122876304</v>
+        <v>1.703957539257788</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.152774123906802</v>
+        <v>-9.005206326246533</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5131331296021089</v>
+        <v>-0.454106010538001</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.282106750787495</v>
+        <v>-2.282737723485021</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.779068893801863</v>
+        <v>1.778690310183347</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.962174449233649</v>
+        <v>-8.81460665157338</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4340781990452105</v>
+        <v>-0.3750510799811031</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.091507076114343</v>
+        <v>-2.092138048811868</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.896243759293391</v>
+        <v>1.895865175674876</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.713174650550068</v>
+        <v>-8.565606852889799</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3215719383481193</v>
+        <v>-0.2625448192840119</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.091507076114343</v>
+        <v>-2.092138048811868</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.909150100517049</v>
+        <v>1.908771516898534</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.818764640323172</v>
+        <v>-8.671196842662903</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4917838638565799</v>
+        <v>-0.4327567447924725</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.197097065887447</v>
+        <v>-2.197728038584973</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.717820177053968</v>
+        <v>1.717441593435453</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.837499542441769</v>
+        <v>-8.6899317447815</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4507334828269323</v>
+        <v>-0.3917063637628249</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.197097065887447</v>
+        <v>-2.197728038584973</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.766364518931055</v>
+        <v>1.765985935312539</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.68955950103417</v>
+        <v>-8.541991703373901</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5114363889520601</v>
+        <v>-0.4524092698879527</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.17677614997889</v>
+        <v>-2.177407122676415</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.658678145788022</v>
+        <v>1.658299562169506</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.665330864645197</v>
+        <v>-8.517763066984928</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5104589206499495</v>
+        <v>-0.4514318015858416</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.152547513589917</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.664501341367927</v>
+        <v>1.664122757749412</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.621782457874506</v>
+        <v>-8.474214660214237</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.500000170036766</v>
+        <v>-0.4409730509726586</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.152547513589917</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.657540729272833</v>
+        <v>1.657162145654318</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.379634064420648</v>
+        <v>-8.232066266760379</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3886784582740797</v>
+        <v>-0.3296513392099722</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.152547513589917</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.672003083653977</v>
+        <v>1.671624500035461</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.82854791119282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.3164046926523</v>
+        <v>-8.168836894992031</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3688545891075456</v>
+        <v>-0.3098274700434382</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.152547513589917</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.666535204113172</v>
+        <v>1.666156620494657</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.19311355783517</v>
+        <v>-8.045545760174901</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.322040041170117</v>
+        <v>-0.2630129221060091</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.029256378772787</v>
+        <v>-2.029887351470312</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.738007979014027</v>
+        <v>1.737629395395512</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389913</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.171964358931728</v>
+        <v>-8.024396561271459</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3058793833714146</v>
+        <v>-0.2468522643073072</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.008107179869344</v>
+        <v>-2.008738152566869</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.758398476593418</v>
+        <v>1.758019892974903</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.928198916948284</v>
+        <v>-7.780631119288015</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2125924982309861</v>
+        <v>-0.1535653791668787</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.008107179869344</v>
+        <v>-2.008738152566869</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.754179184940469</v>
+        <v>1.753800601321953</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.664170849755024</v>
+        <v>-7.516603052094755</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1048569574336664</v>
+        <v>-0.04582983836955901</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.80624178105339</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.877422738150057</v>
+        <v>1.877044154531541</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.414320455805949</v>
+        <v>-7.26675265814568</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.01217472487033433</v>
+        <v>0.04685239419377307</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.80624178105339</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.870164813133759</v>
+        <v>1.869786229515244</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.238428363338517</v>
+        <v>-7.090860565678248</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.06178123563728732</v>
+        <v>0.1208083547013947</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.80624178105339</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.873763936654408</v>
+        <v>1.873385353035892</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.78093033586299</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.164948454486503</v>
+        <v>-7.017380656826234</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1045007052326468</v>
+        <v>0.1635278242967542</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.732761872201376</v>
+        <v>-1.733392844898901</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.93117938802017</v>
+        <v>1.930800804401655</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.93991545481768</v>
+        <v>-6.792347657157411</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.1935343827164728</v>
+        <v>0.2525615017805807</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.507728872532553</v>
+        <v>-1.508359845230078</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.065219665437761</v>
+        <v>2.064841081819246</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.725281077181273</v>
+        <v>-6.577713279521004</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2840829348253529</v>
+        <v>0.3431100538894607</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.293094494896146</v>
+        <v>-1.293725467593672</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.198695093073922</v>
+        <v>2.198316509455407</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.458680720206921</v>
+        <v>-6.311112922546652</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3719173363988895</v>
+        <v>0.4309444554629969</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.293094494896146</v>
+        <v>-1.293725467593672</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.179889351857717</v>
+        <v>2.179510768239203</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712298</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.218250223402061</v>
+        <v>-6.070682425741792</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4698326117457108</v>
+        <v>0.5288597308098182</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.052663998091286</v>
+        <v>-1.053294970788811</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.325890726565511</v>
+        <v>2.325512142946996</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.975459415752615</v>
+        <v>-5.827891618092346</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5708782486403092</v>
+        <v>0.6299053677044166</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.052663998091286</v>
+        <v>-1.053294970788811</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.329820040400331</v>
+        <v>2.329441456781816</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.85951956612743</v>
+        <v>-5.711951768467161</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6179327724077233</v>
+        <v>0.6769598914718311</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9758422670751621</v>
+        <v>-0.9764732397726874</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.376591662927346</v>
+        <v>2.376213079308831</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972344</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.616863977704266</v>
+        <v>-5.469296180043997</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7119930789969824</v>
+        <v>0.7710201980610898</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9758422670751621</v>
+        <v>-0.9764732397726874</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.373589734147339</v>
+        <v>2.373211150528824</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.396843179667256</v>
+        <v>-5.249275382006987</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8015804352224007</v>
+        <v>0.8606075542865081</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8346224220071818</v>
+        <v>-0.8352533947047072</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.459900678198741</v>
+        <v>2.459522094580226</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009955</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.197594549762447</v>
+        <v>-5.050026752102178</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8971740699861477</v>
+        <v>0.9562011890502551</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8346224220071818</v>
+        <v>-0.8352533947047072</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.475794861000565</v>
+        <v>2.475416277382049</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.038079446243077</v>
+        <v>-4.890511648582808</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9621259558341975</v>
+        <v>1.021153074898305</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6751073184878119</v>
+        <v>-0.6757382911853372</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.572649767552488</v>
+        <v>2.572271183933974</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976047</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.893407301143339</v>
+        <v>-4.74583950348307</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.030082916435532</v>
+        <v>1.08911003549964</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5304351733880746</v>
+        <v>-0.5310661460855999</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.669541157173771</v>
+        <v>2.669162573555256</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412108</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.953282128501032</v>
+        <v>-4.805714330840763</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.992170476893881</v>
+        <v>1.051197595957989</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5903100007457667</v>
+        <v>-0.590940973443292</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.619653752160581</v>
+        <v>2.619275168542066</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144521</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.866482630722023</v>
+        <v>-4.718914833061755</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.049290769328051</v>
+        <v>1.108317888392158</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5903100007457667</v>
+        <v>-0.590940973443292</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.642054245483147</v>
+        <v>2.641675661864632</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.868952337183829</v>
+        <v>-4.721384539523561</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.04837528811674</v>
+        <v>1.107402407180848</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5927797072075729</v>
+        <v>-0.5934106799050982</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.640644822979476</v>
+        <v>2.640266239360961</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.93732252350784</v>
+        <v>-4.789754725847571</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.032034136061838</v>
+        <v>1.091061255125946</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5835040081713579</v>
+        <v>-0.5841349808688833</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.657217164875907</v>
+        <v>2.656838581257392</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978374</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.815906093881363</v>
+        <v>-4.668338296221094</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.07103741654432</v>
+        <v>1.130064535608428</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5835040081713579</v>
+        <v>-0.5841349808688833</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.647653873507798</v>
+        <v>2.647275289889283</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.846899253210069</v>
+        <v>-4.6993314555498</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8833497178532248</v>
+        <v>0.9423768369173324</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5835040081713579</v>
+        <v>-0.5841349808688833</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.472363438548185</v>
+        <v>2.47198485492967</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675906</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.671424993417599</v>
+        <v>-4.52385719575733</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9581066537620004</v>
+        <v>1.017133772826108</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5835040081713579</v>
+        <v>-0.5841349808688833</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.476930670539973</v>
+        <v>2.476552086921457</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695452</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.782361246058848</v>
+        <v>-4.634793448398579</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9137436265922985</v>
+        <v>0.9727707456564061</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5835040081713579</v>
+        <v>-0.5841349808688833</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.47694214442677</v>
+        <v>2.476563560808255</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.985387823602081</v>
+        <v>-4.837820025941812</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8356643807949107</v>
+        <v>0.8946914998590183</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7865305857145913</v>
+        <v>-0.7871615584121167</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.358257583120736</v>
+        <v>2.35787899950222</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734167</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.827462224666788</v>
+        <v>-4.679894427006519</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9090070068011602</v>
+        <v>0.9680341258652678</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7865305857145913</v>
+        <v>-0.7871615584121167</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.368429969552868</v>
+        <v>2.368051385934353</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212303</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.975783478477917</v>
+        <v>-4.828215680817648</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8446247758505692</v>
+        <v>0.9036518949146766</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7865305857145913</v>
+        <v>-0.7871615584121167</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.363376240126728</v>
+        <v>2.362997656508213</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.976966563128977</v>
+        <v>-4.829398765468708</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8359273174346704</v>
+        <v>0.894954436498778</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7921736341811029</v>
+        <v>-0.7928046068786282</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.351766186491347</v>
+        <v>2.351387602872832</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.853838856134894</v>
+        <v>-4.706271058474625</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8857302732654051</v>
+        <v>0.9447573923295127</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7921736341811029</v>
+        <v>-0.7928046068786282</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.352318059524449</v>
+        <v>2.351939475905934</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279505</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.761028374684035</v>
+        <v>-4.613460577023766</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8521271577371148</v>
+        <v>0.9111542768012222</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6993631527302435</v>
+        <v>-0.6999941254277688</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.33727704028633</v>
+        <v>2.336898456667815</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.712465322463005</v>
+        <v>-4.564897524802736</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8734258545501274</v>
+        <v>0.9324529736142351</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6508001005092133</v>
+        <v>-0.6514310732067387</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.368288347543549</v>
+        <v>2.367909763925033</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.599794104226754</v>
+        <v>-4.452226306566486</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9135700503563506</v>
+        <v>0.972597169420458</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5381288822729631</v>
+        <v>-0.5387598549704884</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.430966786997022</v>
+        <v>2.430588203378507</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268542</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.487417103044081</v>
+        <v>-4.339849305383813</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9640121466600871</v>
+        <v>1.023039265724194</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5381288822729631</v>
+        <v>-0.5387598549704884</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.436458082827689</v>
+        <v>2.436079499209174</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.685651671930812</v>
+        <v>-4.538083874270543</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8962155208739337</v>
+        <v>0.9552426399380414</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7363634511596937</v>
+        <v>-0.736994423857219</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.32901454326419</v>
+        <v>2.328635959645675</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,45 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.351838675471003</v>
+        <v>3.643066046175329</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.768652952956091</v>
+        <v>-4.528641496063044</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7013707284644755</v>
+        <v>0.7973753112216941</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7549343356868674</v>
+        <v>-0.7312285388688564</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.156227732548539</v>
+        <v>2.170451210639345</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="2" t="n">
+        <v>45414</v>
+      </c>
+      <c r="B1952" t="n">
+        <v>3.707270870167442</v>
+      </c>
+      <c r="C1952" t="n">
+        <v>2.703029525374801</v>
+      </c>
+      <c r="D1952" t="n">
+        <v>-4.528641496063044</v>
+      </c>
+      <c r="E1952" t="n">
+        <v>0.7973753112216941</v>
+      </c>
+      <c r="F1952" t="n">
+        <v>-0.7312285388688564</v>
+      </c>
+      <c r="G1952" t="n">
+        <v>2.696093322361169</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-62.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-81.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.2%</t>
+          <t>439.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.4%</t>
+          <t>-630.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-120.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-296.5%</t>
+          <t>-302.8%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-297.1%</t>
+          <t>-297.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.4%</t>
+          <t>-197.3%</t>
         </is>
       </c>
     </row>
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.95311252485442</v>
+        <v>-12.11103323748383</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.60575080046231</v>
+        <v>-1.668919085514073</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.323727438065055</v>
+        <v>-3.326961173139873</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.181614170954172</v>
+        <v>1.179673929909281</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.66683771253172</v>
+        <v>-11.82475842516113</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.490101730977174</v>
+        <v>-1.553270016028936</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.323727438065055</v>
+        <v>-3.326961173139873</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.182753315510231</v>
+        <v>1.18081307446534</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.71973300057601</v>
+        <v>-11.87765371320542</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.50862607203278</v>
+        <v>-1.571794357084544</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.318772091976609</v>
+        <v>-3.322005827051427</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.188360297325406</v>
+        <v>1.186420056280515</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.43582426964726</v>
+        <v>-11.59374498227667</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.389328875422644</v>
+        <v>-1.452497160474407</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.318772091976609</v>
+        <v>-3.322005827051427</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.194094001564043</v>
+        <v>1.192153760519152</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.32040334550917</v>
+        <v>-11.47832405813857</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.352897768161271</v>
+        <v>-1.416066053213035</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.206584902913331</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.253609293653035</v>
+        <v>1.251669052608144</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.0565664783051</v>
+        <v>-11.2144871909345</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.257246502592551</v>
+        <v>-1.320414787644314</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.206584902913331</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.243725812340127</v>
+        <v>1.241785571295237</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.7893246774367</v>
+        <v>-10.94724539006611</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.152184342744565</v>
+        <v>-1.215352627796328</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.206584902913331</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.241891251840753</v>
+        <v>1.239951010795863</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.66601874895848</v>
+        <v>-10.82393946158789</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.103162286326738</v>
+        <v>-1.166330571378502</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.11393349671095</v>
+        <v>-3.117167231785768</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.29524153954383</v>
+        <v>1.29330129849894</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.64206520798252</v>
+        <v>-10.79998592061193</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.092912363790862</v>
+        <v>-1.156080648842625</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.089979955734993</v>
+        <v>-3.093213690809811</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.310282170274899</v>
+        <v>1.308341929230008</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.37800526965972</v>
+        <v>-10.53592598228913</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.000548704623495</v>
+        <v>-1.063716989675259</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.825920017412197</v>
+        <v>-2.829153752487014</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.455457817106824</v>
+        <v>1.453517576061934</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.670925646154886</v>
+        <v>-9.828846358784295</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7205038888818609</v>
+        <v>-0.7836721739336245</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.825920017412197</v>
+        <v>-2.829153752487014</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.452670783446523</v>
+        <v>1.450730542401633</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.630741347788696</v>
+        <v>-9.788662060418105</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7040865456475434</v>
+        <v>-0.767254830699307</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.785735719046006</v>
+        <v>-2.788969454120823</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.477124986354079</v>
+        <v>1.475184745309189</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.550671552250892</v>
+        <v>-9.7085922648803</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6726918062116649</v>
+        <v>-0.7358600912634281</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.705665923508202</v>
+        <v>-2.708899658583019</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.524533684897519</v>
+        <v>1.522593443852628</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.317190330021294</v>
+        <v>-9.475111042650703</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5713748884819734</v>
+        <v>-0.6345431735337366</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.472184701278603</v>
+        <v>-2.475418436353421</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.67254684707313</v>
+        <v>1.670606606028239</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.13748179987742</v>
+        <v>-9.295402512506829</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.502383686737383</v>
+        <v>-0.5655519717891466</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.415013197115907</v>
+        <v>-2.418246932190725</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.703957539257788</v>
+        <v>1.702017298212898</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.005206326246533</v>
+        <v>-9.163127038875942</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.454106010538001</v>
+        <v>-0.5172742955897647</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.282737723485021</v>
+        <v>-2.285971458559839</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.778690310183347</v>
+        <v>1.776750069138457</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.81460665157338</v>
+        <v>-8.972527364202788</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3750510799811031</v>
+        <v>-0.4382193650328663</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.092138048811868</v>
+        <v>-2.095371783886686</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.895865175674876</v>
+        <v>1.893924934629985</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.565606852889799</v>
+        <v>-8.723527565519207</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2625448192840119</v>
+        <v>-0.3257131043357755</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.092138048811868</v>
+        <v>-2.095371783886686</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.908771516898534</v>
+        <v>1.906831275853644</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.671196842662903</v>
+        <v>-8.829117555292312</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4327567447924725</v>
+        <v>-0.4959250298442357</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.197728038584973</v>
+        <v>-2.20096177365979</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.717441593435453</v>
+        <v>1.715501352390562</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.6899317447815</v>
+        <v>-8.847852457410909</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3917063637628249</v>
+        <v>-0.4548746488145881</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.197728038584973</v>
+        <v>-2.20096177365979</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.765985935312539</v>
+        <v>1.764045694267649</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.541991703373901</v>
+        <v>-8.699912416003309</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4524092698879527</v>
+        <v>-0.5155775549397159</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.177407122676415</v>
+        <v>-2.180640857751233</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.658299562169506</v>
+        <v>1.656359321124616</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.517763066984928</v>
+        <v>-8.675683779614337</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4514318015858416</v>
+        <v>-0.5146000866376053</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.156412221362261</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.664122757749412</v>
+        <v>1.662182516704521</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.474214660214237</v>
+        <v>-8.632135372843646</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4409730509726586</v>
+        <v>-0.5041413360244218</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.156412221362261</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.657162145654318</v>
+        <v>1.655221904609428</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.232066266760379</v>
+        <v>-8.389986979389787</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3296513392099722</v>
+        <v>-0.3928196242617354</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.156412221362261</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.671624500035461</v>
+        <v>1.669684258990571</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.168836894992031</v>
+        <v>-8.32675760762144</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3098274700434382</v>
+        <v>-0.3729957550952014</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.156412221362261</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.666156620494657</v>
+        <v>1.664216379449766</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.045545760174901</v>
+        <v>-8.20346647280431</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2630129221060091</v>
+        <v>-0.3261812071577728</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.029887351470312</v>
+        <v>-2.03312108654513</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.737629395395512</v>
+        <v>1.735689154350621</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.024396561271459</v>
+        <v>-8.182317273900868</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2468522643073072</v>
+        <v>-0.3100205493590704</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.008738152566869</v>
+        <v>-2.011971887641687</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.758019892974903</v>
+        <v>1.756079651930012</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.780631119288015</v>
+        <v>-7.938551831917423</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1535653791668787</v>
+        <v>-0.2167336642186419</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.008738152566869</v>
+        <v>-2.011971887641687</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.753800601321953</v>
+        <v>1.751860360277063</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.516603052094755</v>
+        <v>-7.674523764724164</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.04582983836955901</v>
+        <v>-0.1089981234213222</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.810106488825733</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.877044154531541</v>
+        <v>1.875103913486651</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.26675265814568</v>
+        <v>-7.424673370775089</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.04685239419377307</v>
+        <v>-0.01631589085799012</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.810106488825733</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.869786229515244</v>
+        <v>1.867845988470353</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.090860565678248</v>
+        <v>-7.248781278307657</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1208083547013947</v>
+        <v>0.05764006964963109</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.810106488825733</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.873385353035892</v>
+        <v>1.871445111991002</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.017380656826234</v>
+        <v>-7.175301369455642</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1635278242967542</v>
+        <v>0.100359539244991</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.733392844898901</v>
+        <v>-1.736626579973719</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.930800804401655</v>
+        <v>1.928860563356764</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.792347657157411</v>
+        <v>-6.950268369786819</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2525615017805807</v>
+        <v>0.189393216728817</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.508359845230078</v>
+        <v>-1.511593580304896</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.064841081819246</v>
+        <v>2.062900840774355</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.577713279521004</v>
+        <v>-6.735633992150412</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3431100538894607</v>
+        <v>0.2799417688376971</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.293725467593672</v>
+        <v>-1.296959202668489</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.198316509455407</v>
+        <v>2.196376268410516</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.311112922546652</v>
+        <v>-6.469033635176061</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4309444554629969</v>
+        <v>0.3677761704112332</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.293725467593672</v>
+        <v>-1.296959202668489</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.179510768239203</v>
+        <v>2.177570527194312</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.070682425741792</v>
+        <v>-6.2286031383712</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5288597308098182</v>
+        <v>0.465691445758055</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.053294970788811</v>
+        <v>-1.056528705863629</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.325512142946996</v>
+        <v>2.323571901902105</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.827891618092346</v>
+        <v>-5.985812330721755</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6299053677044166</v>
+        <v>0.5667370826526534</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.053294970788811</v>
+        <v>-1.056528705863629</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.329441456781816</v>
+        <v>2.327501215736925</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.711951768467161</v>
+        <v>-5.86987248109657</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6769598914718311</v>
+        <v>0.6137916064200675</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9764732397726874</v>
+        <v>-0.9797069748475051</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.376213079308831</v>
+        <v>2.37427283826394</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.469296180043997</v>
+        <v>-5.627216892673406</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7710201980610898</v>
+        <v>0.7078519130093266</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9764732397726874</v>
+        <v>-0.9797069748475051</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.373211150528824</v>
+        <v>2.371270909483933</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.249275382006987</v>
+        <v>-5.407196094636396</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8606075542865081</v>
+        <v>0.797439269234745</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8352533947047072</v>
+        <v>-0.8384871297795249</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.459522094580226</v>
+        <v>2.457581853535336</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.050026752102178</v>
+        <v>-5.207947464731586</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9562011890502551</v>
+        <v>0.8930329039984919</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8352533947047072</v>
+        <v>-0.8384871297795249</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.475416277382049</v>
+        <v>2.473476036337159</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.890511648582808</v>
+        <v>-5.048432361212217</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.021153074898305</v>
+        <v>0.9579847898465417</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6757382911853372</v>
+        <v>-0.678972026260155</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.572271183933974</v>
+        <v>2.570330942889083</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.74583950348307</v>
+        <v>-4.903760216112479</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.08911003549964</v>
+        <v>1.025941750447876</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5310661460855999</v>
+        <v>-0.5342998811604176</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.669162573555256</v>
+        <v>2.667222332510365</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.805714330840763</v>
+        <v>-4.963635043470171</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.051197595957989</v>
+        <v>0.9880293109062253</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.590940973443292</v>
+        <v>-0.5941747085181097</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.619275168542066</v>
+        <v>2.617334927497176</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.718914833061755</v>
+        <v>-4.876835545691163</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.108317888392158</v>
+        <v>1.045149603340395</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.590940973443292</v>
+        <v>-0.5941747085181097</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.641675661864632</v>
+        <v>2.639735420819742</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.721384539523561</v>
+        <v>-4.879305252152969</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.107402407180848</v>
+        <v>1.044234122129085</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5934106799050982</v>
+        <v>-0.5966444149799159</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.640266239360961</v>
+        <v>2.63832599831607</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.789754725847571</v>
+        <v>-4.947675438476979</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.091061255125946</v>
+        <v>1.027892970074182</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.587368715943701</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.656838581257392</v>
+        <v>2.654898340212501</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.668338296221094</v>
+        <v>-4.826259008850503</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.130064535608428</v>
+        <v>1.066896250556664</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.587368715943701</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.647275289889283</v>
+        <v>2.645335048844392</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.6993314555498</v>
+        <v>-4.857252168179208</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9423768369173324</v>
+        <v>0.879208551865569</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.587368715943701</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.47198485492967</v>
+        <v>2.470044613884779</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.52385719575733</v>
+        <v>-4.681777908386739</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.017133772826108</v>
+        <v>0.9539654877743446</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.587368715943701</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.476552086921457</v>
+        <v>2.474611845876567</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.634793448398579</v>
+        <v>-4.792714161027988</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9727707456564061</v>
+        <v>0.9096024606046424</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5841349808688833</v>
+        <v>-0.587368715943701</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.476563560808255</v>
+        <v>2.474623319763364</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.837820025941812</v>
+        <v>-4.995740738571221</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8946914998590183</v>
+        <v>0.8315232148072549</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7871615584121167</v>
+        <v>-0.7903952934869344</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.35787899950222</v>
+        <v>2.35593875845733</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.679894427006519</v>
+        <v>-4.837815139635928</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9680341258652678</v>
+        <v>0.9048658408135044</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7871615584121167</v>
+        <v>-0.7903952934869344</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.368051385934353</v>
+        <v>2.366111144889462</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.828215680817648</v>
+        <v>-4.986136393447056</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9036518949146766</v>
+        <v>0.8404836098629132</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7871615584121167</v>
+        <v>-0.7903952934869344</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.362997656508213</v>
+        <v>2.361057415463323</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.829398765468708</v>
+        <v>-4.987319478098117</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.894954436498778</v>
+        <v>0.8317861514470146</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7928046068786282</v>
+        <v>-0.7960383419534459</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.351387602872832</v>
+        <v>2.349447361827941</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.706271058474625</v>
+        <v>-4.864191771104034</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9447573923295127</v>
+        <v>0.8815891072777493</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7928046068786282</v>
+        <v>-0.7960383419534459</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.351939475905934</v>
+        <v>2.349999234861043</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.613460577023766</v>
+        <v>-4.771381289653174</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9111542768012222</v>
+        <v>0.8479859917494588</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6999941254277688</v>
+        <v>-0.7032278605025866</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.336898456667815</v>
+        <v>2.334958215622924</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.564897524802736</v>
+        <v>-4.722818237432144</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9324529736142351</v>
+        <v>0.8692846885624717</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6514310732067387</v>
+        <v>-0.6546648082815564</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.367909763925033</v>
+        <v>2.365969522880143</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.452226306566486</v>
+        <v>-4.610147019195894</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.972597169420458</v>
+        <v>0.9094288843686946</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5387598549704884</v>
+        <v>-0.5419935900453061</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.430588203378507</v>
+        <v>2.428647962333616</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.339849305383813</v>
+        <v>-4.497770018013221</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.023039265724194</v>
+        <v>0.959870980672431</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5387598549704884</v>
+        <v>-0.5419935900453061</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.436079499209174</v>
+        <v>2.434139258164283</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.538083874270543</v>
+        <v>-4.696004586899952</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9552426399380414</v>
+        <v>0.8920743548862777</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.736994423857219</v>
+        <v>-0.7402281589320368</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.328635959645675</v>
+        <v>2.326695718600784</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.528641496063044</v>
+        <v>-4.686562208692453</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7973753112216941</v>
+        <v>0.7342070261699307</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7312285388688564</v>
+        <v>-0.7344622739436741</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.170451210639345</v>
+        <v>2.168510969594455</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.707270870167442</v>
+        <v>3.337627147568574</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.703029525374801</v>
+        <v>2.494426208511203</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.528641496063044</v>
+        <v>-4.686562208692453</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7973753112216941</v>
+        <v>0.7342070261699307</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7312285388688564</v>
+        <v>-0.7344622739436741</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.696093322361169</v>
+        <v>2.487490005497571</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,55 +811,55 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-62.2%</t>
+          <t>-29.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-708.7%</t>
+          <t>-682.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-54.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.4%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.2%</t>
+          <t>-611.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-273.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-42.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-120.9%</t>
+          <t>-54.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-302.8%</t>
+          <t>-295.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-332.9%</t>
+          <t>-322.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-164.2%</t>
+          <t>-156.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-297.4%</t>
+          <t>-288.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-200.1%</t>
+          <t>-193.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-197.3%</t>
+          <t>-164.6%</t>
         </is>
       </c>
     </row>
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.916479404131921</v>
+        <v>-2.650592796064066</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.971493420929135</v>
+        <v>2.077848064156277</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.00120423626735916</v>
+        <v>0.1082200424992689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.137719065135235</v>
+        <v>3.203373632395212</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.408864432156018</v>
+        <v>-3.142977824088163</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.775645801763228</v>
+        <v>1.88200044499037</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4935892642914559</v>
+        <v>-0.3841649855248279</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.843394440364509</v>
+        <v>2.909049007624486</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.79404482308609</v>
+        <v>-3.528158215018236</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.620116184204063</v>
+        <v>1.726470827431204</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4935892642914559</v>
+        <v>-0.3841649855248279</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.841936979177373</v>
+        <v>2.90759154643735</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.137727596312753</v>
+        <v>-3.871840988244898</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.484412198368014</v>
+        <v>1.590766841595156</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.601495316318674</v>
+        <v>-0.4920710375520461</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.778962471415658</v>
+        <v>2.844617038675635</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.495377946551101</v>
+        <v>-4.229491338483246</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.337458116928932</v>
+        <v>1.443812760156074</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9591456665570222</v>
+        <v>-0.8497213877903942</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.560478319928907</v>
+        <v>2.626132887188884</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.804612049547152</v>
+        <v>-4.538725441479297</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.215537402430771</v>
+        <v>1.321892045657913</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9591456665570222</v>
+        <v>-0.8497213877903942</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.562251246629166</v>
+        <v>2.627905813889143</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.236417842696939</v>
+        <v>-4.970531234629084</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.029147972638261</v>
+        <v>1.135502615865403</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.095563162998289</v>
+        <v>-0.9861388842316612</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.466733636231811</v>
+        <v>2.532388203491788</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.471111836829492</v>
+        <v>-5.205225228761637</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9235551499873305</v>
+        <v>1.029909793214473</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.089226895769034</v>
+        <v>-0.979802617002406</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.458820171571454</v>
+        <v>2.524474738831431</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.806774484059944</v>
+        <v>-5.540887875992089</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7878706827511146</v>
+        <v>0.8942253259782569</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.089226895769034</v>
+        <v>-0.979802617002406</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.45740076322742</v>
+        <v>2.523055330487396</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.170400728960257</v>
+        <v>-5.904514120892403</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6489077450252307</v>
+        <v>0.755262388252373</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.18744853263616</v>
+        <v>-1.078024253869532</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.404955341341386</v>
+        <v>2.470609908601363</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.535528111599004</v>
+        <v>-6.269641503531149</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5021113069755638</v>
+        <v>0.6084659502027057</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.483759316935172</v>
+        <v>-1.374335038168544</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.226423385767809</v>
+        <v>2.292077953027786</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.944116888779682</v>
+        <v>-6.678230280711828</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3374373401180515</v>
+        <v>0.4437919833451929</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.782923815349223</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.980031663474161</v>
+        <v>2.045686230734138</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.357099372920776</v>
+        <v>-7.091212764852922</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1674297789330748</v>
+        <v>0.2737844221602161</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.782923815349223</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.975217095945622</v>
+        <v>2.040871663205599</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.773491247207773</v>
+        <v>-7.507604639139919</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.001132920172846941</v>
+        <v>0.1052217230542944</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.782923815349223</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.973211146554499</v>
+        <v>2.038865713814476</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.150168257737617</v>
+        <v>-7.884281649669764</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1415450337161053</v>
+        <v>-0.03519039048896433</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.782923815349223</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.983469837223178</v>
+        <v>2.049124404483155</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.496043079722426</v>
+        <v>-8.230156471654572</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2837953973643339</v>
+        <v>-0.1774407541371925</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.782923815349223</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.979569402368874</v>
+        <v>2.045223969628851</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.658185350185519</v>
+        <v>-8.392298742117665</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3502473854945705</v>
+        <v>-0.2438927422674286</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.782923815349223</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.977974322423875</v>
+        <v>2.043628889683851</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.954846691995717</v>
+        <v>-8.688960083927864</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4651329462894416</v>
+        <v>-0.3587783030622997</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.961091229849729</v>
+        <v>-1.851666951083101</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.940507416912756</v>
+        <v>2.006161984172732</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.388195800105953</v>
+        <v>-9.122309192038099</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6424988940679386</v>
+        <v>-0.5361442508407972</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.961091229849729</v>
+        <v>-1.851666951083101</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.936481112378353</v>
+        <v>2.00213567963833</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.771197188848584</v>
+        <v>-9.50531058078073</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.795801550886575</v>
+        <v>-0.6894469076594336</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.961091229849729</v>
+        <v>-1.851666951083101</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.936379011056768</v>
+        <v>2.002033578316746</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.928596069061705</v>
+        <v>-9.662709460993851</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8561895870003933</v>
+        <v>-0.7498349437732519</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.11849011006285</v>
+        <v>-2.009065831296223</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.844511198900326</v>
+        <v>1.910165766160303</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.28812639156571</v>
+        <v>-10.02223978349785</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9946514127039441</v>
+        <v>-0.8882967694768018</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.11849011006285</v>
+        <v>-2.009065831296223</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.849861502198376</v>
+        <v>1.915516069458353</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.61452642023072</v>
+        <v>-10.34863981216287</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.117295404212772</v>
+        <v>-1.01094076098563</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.444890138727863</v>
+        <v>-2.335465859961236</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.661937504956546</v>
+        <v>1.727592072216523</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.83367538830492</v>
+        <v>-10.56778878023706</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.201913240820681</v>
+        <v>-1.09555859759354</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.664039106802061</v>
+        <v>-2.554614828035433</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.533489874733796</v>
+        <v>1.599144441993773</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407496</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.82998446334851</v>
+        <v>-10.56409785528065</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.200436870838117</v>
+        <v>-1.094082227610976</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.664039106802061</v>
+        <v>-2.554614828035433</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.533489874733796</v>
+        <v>1.599144441993773</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611699</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.03424263867837</v>
+        <v>-10.76835603061052</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.27662694385142</v>
+        <v>-1.170272300624279</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.79167805141605</v>
+        <v>-2.682253772649422</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.462419705084045</v>
+        <v>1.528074272344022</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49684832919989</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.25228041030955</v>
+        <v>-10.98639380224169</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.359359498019455</v>
+        <v>-1.253004854792314</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.966448819511949</v>
+        <v>-2.857024540745321</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.362039798710942</v>
+        <v>1.427694365970919</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910633</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.1788105786421</v>
+        <v>-10.91292397057424</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.314599863859055</v>
+        <v>-1.208245220631913</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.8929789878445</v>
+        <v>-2.783554709077873</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.421493399204832</v>
+        <v>1.487147966464809</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.35393499602864</v>
+        <v>-11.08804838796079</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.370094410066155</v>
+        <v>-1.263739766839014</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.068103405231044</v>
+        <v>-2.958679126464416</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.330973969520423</v>
+        <v>1.3966285367804</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.58838709004313</v>
+        <v>-11.32250048197528</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.471094412573547</v>
+        <v>-1.364739769346406</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.068103405231044</v>
+        <v>-2.958679126464416</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.323754804618827</v>
+        <v>1.389409371878804</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.87619093458037</v>
+        <v>-11.61030432651252</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.592888141162419</v>
+        <v>-1.486533497935277</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.355907249768282</v>
+        <v>-3.246482971001655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.144400307122508</v>
+        <v>1.210054874382485</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.10601538174419</v>
+        <v>-11.84012877367634</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.683702130189393</v>
+        <v>-1.577347486962251</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.518554786838443</v>
+        <v>-3.409130508071815</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.047927574718968</v>
+        <v>1.113582141978945</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.33804430148046</v>
+        <v>-12.0721576934126</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.773819969454782</v>
+        <v>-1.667465326227641</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.580567484026866</v>
+        <v>-3.471143205260238</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.013413685035028</v>
+        <v>1.079068252295005</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.28602878751164</v>
+        <v>-12.02014217944379</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.749023428180856</v>
+        <v>-1.642668784953715</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.580567484026866</v>
+        <v>-3.471143205260238</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.017404020721429</v>
+        <v>1.083058587981406</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.42770062923576</v>
+        <v>-12.16181402116791</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.807167391769246</v>
+        <v>-1.700812748542105</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.580567484026866</v>
+        <v>-3.471143205260238</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.015928793822687</v>
+        <v>1.081583361082664</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.37810978481093</v>
+        <v>-12.11222317674308</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.77227764383444</v>
+        <v>-1.665923000607299</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.530976639602032</v>
+        <v>-3.421552360835404</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.06073671064246</v>
+        <v>1.126391277902437</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.17895767757383</v>
+        <v>-11.91307106950598</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.705667934586284</v>
+        <v>-1.599313291359142</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.365654113652219</v>
+        <v>-3.256229834885591</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.146879092565665</v>
+        <v>1.212533659825642</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.11103323748383</v>
+        <v>-11.83479371444683</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.668919085514073</v>
+        <v>-1.558423276299276</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.326961173139873</v>
+        <v>-3.213672186600902</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.179673929909281</v>
+        <v>1.247647321832664</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.82475842516113</v>
+        <v>-11.54851890212414</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.553270016028936</v>
+        <v>-1.44277420681414</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.326961173139873</v>
+        <v>-3.213672186600902</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.18081307446534</v>
+        <v>1.248786466388723</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.87765371320542</v>
+        <v>-11.60141419016843</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.571794357084544</v>
+        <v>-1.461298547869746</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.322005827051427</v>
+        <v>-3.208716840512456</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.186420056280515</v>
+        <v>1.254393448203899</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.59374498227667</v>
+        <v>-11.31750545923968</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.452497160474407</v>
+        <v>-1.342001351259611</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.322005827051427</v>
+        <v>-3.208716840512456</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.192153760519152</v>
+        <v>1.260127152442535</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.47832405813857</v>
+        <v>-11.20208453510158</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.416066053213035</v>
+        <v>-1.305570243998237</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.206584902913331</v>
+        <v>-3.09329591637436</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.251669052608144</v>
+        <v>1.319642444531527</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.2144871909345</v>
+        <v>-10.93824766789751</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.320414787644314</v>
+        <v>-1.209918978429517</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.206584902913331</v>
+        <v>-3.09329591637436</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.241785571295237</v>
+        <v>1.30975896321862</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.94724539006611</v>
+        <v>-10.67100586702911</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.215352627796328</v>
+        <v>-1.104856818581531</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.206584902913331</v>
+        <v>-3.09329591637436</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.239951010795863</v>
+        <v>1.307924402719246</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.82393946158789</v>
+        <v>-10.54769993855089</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.166330571378502</v>
+        <v>-1.055834762163704</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.117167231785768</v>
+        <v>-3.003878245246797</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.29330129849894</v>
+        <v>1.361274690422323</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.79998592061193</v>
+        <v>-10.52374639757494</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.156080648842625</v>
+        <v>-1.045584839627828</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.093213690809811</v>
+        <v>-2.97992470427084</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.308341929230008</v>
+        <v>1.376315321153391</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.53592598228913</v>
+        <v>-10.25968645925214</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.063716989675259</v>
+        <v>-0.9532211804604609</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.829153752487014</v>
+        <v>-2.715864765948043</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.453517576061934</v>
+        <v>1.521490967985316</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.828846358784295</v>
+        <v>-9.552606835747302</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7836721739336245</v>
+        <v>-0.6731763647188269</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.829153752487014</v>
+        <v>-2.715864765948043</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.450730542401633</v>
+        <v>1.518703934325015</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.788662060418105</v>
+        <v>-9.512422537381111</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.767254830699307</v>
+        <v>-0.6567590214845094</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.788969454120823</v>
+        <v>-2.675680467581853</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.475184745309189</v>
+        <v>1.543158137232571</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.7085922648803</v>
+        <v>-9.432352741843307</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7358600912634281</v>
+        <v>-0.6253642820486309</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.708899658583019</v>
+        <v>-2.595610672044049</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.522593443852628</v>
+        <v>1.590566835776011</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761812</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.475111042650703</v>
+        <v>-9.198871519613707</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6345431735337366</v>
+        <v>-0.5240473643189385</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.475418436353421</v>
+        <v>-2.36212944981445</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.670606606028239</v>
+        <v>1.738579997951622</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255789</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.295402512506829</v>
+        <v>-9.019162989469834</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5655519717891466</v>
+        <v>-0.4550561625743486</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.418246932190725</v>
+        <v>-2.304957945651754</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.702017298212898</v>
+        <v>1.769990690136281</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.163127038875942</v>
+        <v>-8.886887515838946</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5172742955897647</v>
+        <v>-0.4067784863749666</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.285971458559839</v>
+        <v>-2.172682472020868</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.776750069138457</v>
+        <v>1.844723461061839</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575957</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.972527364202788</v>
+        <v>-8.696287841165793</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4382193650328663</v>
+        <v>-0.3277235558180682</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.095371783886686</v>
+        <v>-1.982082797347715</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.893924934629985</v>
+        <v>1.961898326553368</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.723527565519207</v>
+        <v>-8.447288042482212</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3257131043357755</v>
+        <v>-0.215217295120977</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.095371783886686</v>
+        <v>-1.982082797347715</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.906831275853644</v>
+        <v>1.974804667777026</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077647</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.829117555292312</v>
+        <v>-8.552878032255316</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4959250298442357</v>
+        <v>-0.3854292206294376</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.20096177365979</v>
+        <v>-2.087672787120819</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.715501352390562</v>
+        <v>1.783474744313945</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.847852457410909</v>
+        <v>-8.571612934373913</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4548746488145881</v>
+        <v>-0.34437883959979</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.20096177365979</v>
+        <v>-2.087672787120819</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.764045694267649</v>
+        <v>1.832019086191032</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180813</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.699912416003309</v>
+        <v>-8.423672892966314</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5155775549397159</v>
+        <v>-0.4050817457249178</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.180640857751233</v>
+        <v>-2.067351871212262</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.656359321124616</v>
+        <v>1.724332713047999</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879206</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.675683779614337</v>
+        <v>-8.399444256577342</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5146000866376053</v>
+        <v>-0.4041042774228072</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.156412221362261</v>
+        <v>-2.04312323482329</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.662182516704521</v>
+        <v>1.730155908627904</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568111</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.632135372843646</v>
+        <v>-8.35589584980665</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5041413360244218</v>
+        <v>-0.3936455268096237</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.156412221362261</v>
+        <v>-2.04312323482329</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.655221904609428</v>
+        <v>1.723195296532811</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963422</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.389986979389787</v>
+        <v>-8.113747456352792</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3928196242617354</v>
+        <v>-0.2823238150469374</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.156412221362261</v>
+        <v>-2.04312323482329</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.669684258990571</v>
+        <v>1.737657650913954</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119282</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.32675760762144</v>
+        <v>-8.050518084584445</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3729957550952014</v>
+        <v>-0.2624999458804034</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.156412221362261</v>
+        <v>-2.04312323482329</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.664216379449766</v>
+        <v>1.732189771373149</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262051</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.20346647280431</v>
+        <v>-7.927226949767314</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3261812071577728</v>
+        <v>-0.2156853979429743</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.03312108654513</v>
+        <v>-1.919832100006159</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.735689154350621</v>
+        <v>1.803662546274004</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389913</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.182317273900868</v>
+        <v>-7.90607775086387</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3100205493590704</v>
+        <v>-0.1995247401442715</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.011971887641687</v>
+        <v>-1.898682901102716</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.756079651930012</v>
+        <v>1.824053043853395</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788097</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.938551831917423</v>
+        <v>-7.662312308880426</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2167336642186419</v>
+        <v>-0.1062378550038434</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.011971887641687</v>
+        <v>-1.898682901102716</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.751860360277063</v>
+        <v>1.819833752200446</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527529</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.674523764724164</v>
+        <v>-7.398284241687167</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1089981234213222</v>
+        <v>0.001497685793476755</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.810106488825733</v>
+        <v>-1.696817502286762</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.875103913486651</v>
+        <v>1.943077305410034</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749187</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.424673370775089</v>
+        <v>-7.148433847738092</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.01631589085799012</v>
+        <v>0.09417991835680839</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.810106488825733</v>
+        <v>-1.696817502286762</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.867845988470353</v>
+        <v>1.935819380393736</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481501</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.248781278307657</v>
+        <v>-6.97254175527066</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.05764006964963109</v>
+        <v>0.16813587886443</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.810106488825733</v>
+        <v>-1.696817502286762</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.871445111991002</v>
+        <v>1.939418503914385</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.78093033586299</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.175301369455642</v>
+        <v>-6.899061846418645</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.100359539244991</v>
+        <v>0.2108553484597899</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.736626579973719</v>
+        <v>-1.623337593434748</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.928860563356764</v>
+        <v>1.996833955280147</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102785</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.950268369786819</v>
+        <v>-6.674028846749822</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.189393216728817</v>
+        <v>0.299889025943616</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.511593580304896</v>
+        <v>-1.398304593765925</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.062900840774355</v>
+        <v>2.130874232697737</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.735633992150412</v>
+        <v>-6.459394469113415</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2799417688376971</v>
+        <v>0.390437578052496</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.296959202668489</v>
+        <v>-1.183670216129519</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.196376268410516</v>
+        <v>2.264349660333899</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.469033635176061</v>
+        <v>-6.192794112139064</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3677761704112332</v>
+        <v>0.4782719796260322</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.296959202668489</v>
+        <v>-1.183670216129519</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.177570527194312</v>
+        <v>2.245543919117694</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712298</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.2286031383712</v>
+        <v>-5.952363615334203</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.465691445758055</v>
+        <v>0.5761872549728539</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.056528705863629</v>
+        <v>-0.9432397193246582</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.323571901902105</v>
+        <v>2.391545293825488</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.985812330721755</v>
+        <v>-5.709572807684758</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5667370826526534</v>
+        <v>0.6772328918674524</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.056528705863629</v>
+        <v>-0.9432397193246582</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.327501215736925</v>
+        <v>2.395474607660308</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.86987248109657</v>
+        <v>-5.593632958059573</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6137916064200675</v>
+        <v>0.7242874156348664</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9797069748475051</v>
+        <v>-0.8664179883085343</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.37427283826394</v>
+        <v>2.442246230187322</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972344</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.627216892673406</v>
+        <v>-5.350977369636409</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7078519130093266</v>
+        <v>0.8183477222241251</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9797069748475051</v>
+        <v>-0.8664179883085343</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.371270909483933</v>
+        <v>2.439244301407316</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.407196094636396</v>
+        <v>-5.130956571599398</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.797439269234745</v>
+        <v>0.9079350784495435</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8384871297795249</v>
+        <v>-0.7251981432405541</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.457581853535336</v>
+        <v>2.525555245458718</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009955</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.207947464731586</v>
+        <v>-4.931707941694589</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8930329039984919</v>
+        <v>1.003528713213291</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8384871297795249</v>
+        <v>-0.7251981432405541</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.473476036337159</v>
+        <v>2.541449428260542</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966263</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.048432361212217</v>
+        <v>-4.772192838175219</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9579847898465417</v>
+        <v>1.06848059906134</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.678972026260155</v>
+        <v>-0.5656830397211842</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.570330942889083</v>
+        <v>2.638304334812466</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976047</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.903760216112479</v>
+        <v>-4.627520693075482</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.025941750447876</v>
+        <v>1.136437559662675</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5342998811604176</v>
+        <v>-0.4210108946214468</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.667222332510365</v>
+        <v>2.735195724433748</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412108</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.963635043470171</v>
+        <v>-4.687395520433174</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9880293109062253</v>
+        <v>1.098525120121024</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5941747085181097</v>
+        <v>-0.4808857219791389</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.617334927497176</v>
+        <v>2.685308319420558</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144521</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.876835545691163</v>
+        <v>-4.600596022654166</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.045149603340395</v>
+        <v>1.155645412555194</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5941747085181097</v>
+        <v>-0.4808857219791389</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.639735420819742</v>
+        <v>2.707708812743125</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900698</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.879305252152969</v>
+        <v>-4.603065729115972</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.044234122129085</v>
+        <v>1.154729931343883</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5966444149799159</v>
+        <v>-0.483355428440945</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.63832599831607</v>
+        <v>2.706299390239453</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473605</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.947675438476979</v>
+        <v>-4.671435915439982</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.027892970074182</v>
+        <v>1.138388779288981</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.587368715943701</v>
+        <v>-0.4740797294047301</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.654898340212501</v>
+        <v>2.722871732135884</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978374</v>
+        <v>3.714175563978373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.826259008850503</v>
+        <v>-4.550019485813506</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.066896250556664</v>
+        <v>1.177392059771463</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.587368715943701</v>
+        <v>-0.4740797294047301</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.645335048844392</v>
+        <v>2.713308440767775</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887708</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.857252168179208</v>
+        <v>-4.581012645142211</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.879208551865569</v>
+        <v>0.9897043610803677</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.587368715943701</v>
+        <v>-0.4740797294047301</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.470044613884779</v>
+        <v>2.538018005808162</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675906</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.681777908386739</v>
+        <v>-4.405538385349741</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9539654877743446</v>
+        <v>1.064461296989143</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.587368715943701</v>
+        <v>-0.4740797294047301</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.474611845876567</v>
+        <v>2.54258523779995</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695452</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.792714161027988</v>
+        <v>-4.51647463799099</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9096024606046424</v>
+        <v>1.020098269819441</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.587368715943701</v>
+        <v>-0.4740797294047301</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.474623319763364</v>
+        <v>2.542596711686747</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581298</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.995740738571221</v>
+        <v>-4.719501215534224</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8315232148072549</v>
+        <v>0.9420190240220536</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7903952934869344</v>
+        <v>-0.6771063069479635</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.35593875845733</v>
+        <v>2.423912150380713</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734167</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.837815139635928</v>
+        <v>-4.561575616598931</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9048658408135044</v>
+        <v>1.015361650028303</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7903952934869344</v>
+        <v>-0.6771063069479635</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.366111144889462</v>
+        <v>2.434084536812845</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212303</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.986136393447056</v>
+        <v>-4.709896870410059</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8404836098629132</v>
+        <v>0.9509794190777121</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7903952934869344</v>
+        <v>-0.6771063069479635</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.361057415463323</v>
+        <v>2.429030807386706</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786051</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.987319478098117</v>
+        <v>-4.71107995506112</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8317861514470146</v>
+        <v>0.9422819606618134</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7960383419534459</v>
+        <v>-0.682749355414475</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.349447361827941</v>
+        <v>2.417420753751324</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273196</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.864191771104034</v>
+        <v>-4.587952248067037</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8815891072777493</v>
+        <v>0.9920849164925483</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7960383419534459</v>
+        <v>-0.682749355414475</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.349999234861043</v>
+        <v>2.417972626784425</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279505</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.771381289653174</v>
+        <v>-4.495141766616177</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8479859917494588</v>
+        <v>0.9584818009642577</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7032278605025866</v>
+        <v>-0.5899388739636157</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.334958215622924</v>
+        <v>2.402931607546307</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030433</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.722818237432144</v>
+        <v>-4.446578714395147</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8692846885624717</v>
+        <v>0.9797804977772704</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6546648082815564</v>
+        <v>-0.5413758217425855</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.365969522880143</v>
+        <v>2.433942914803526</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942745</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.610147019195894</v>
+        <v>-4.333907496158897</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9094288843686946</v>
+        <v>1.019924693583494</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5419935900453061</v>
+        <v>-0.4287046035063353</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.428647962333616</v>
+        <v>2.496621354256999</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268542</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.497770018013221</v>
+        <v>-4.221530494976224</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.959870980672431</v>
+        <v>1.07036678988723</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5419935900453061</v>
+        <v>-0.4287046035063353</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.434139258164283</v>
+        <v>2.502112650087666</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968868</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.696004586899952</v>
+        <v>-4.419765063862955</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8920743548862777</v>
+        <v>1.002570164101077</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7402281589320368</v>
+        <v>-0.6269391723930658</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.326695718600784</v>
+        <v>2.394669110524167</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175329</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.686562208692453</v>
+        <v>-4.502766344888234</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7342070261699307</v>
+        <v>0.8077253716916184</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7344622739436741</v>
+        <v>-0.6455100569202397</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.168510969594455</v>
+        <v>2.221882299808516</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.337627147568574</v>
+        <v>3.883950904316143</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.494426208511203</v>
+        <v>2.821532688588707</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.686562208692453</v>
+        <v>-4.502766344888234</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7342070261699307</v>
+        <v>0.8077253716916184</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7344622739436741</v>
+        <v>-0.6455100569202397</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.487490005497571</v>
+        <v>2.814596485575075</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>114.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-682.1%</t>
+          <t>-681.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>444.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.8%</t>
+          <t>-596.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.2%</t>
+          <t>-273.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-43.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-295.4%</t>
+          <t>-289.4%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-322.0%</t>
+          <t>-322.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-156.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-288.5%</t>
+          <t>-288.7%</t>
         </is>
       </c>
     </row>
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.650592796064066</v>
+        <v>-2.647079875987622</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.077848064156277</v>
+        <v>2.079253232186854</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1082200424992689</v>
+        <v>0.1071529617666157</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.203373632395212</v>
+        <v>3.20273338395562</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.142977824088163</v>
+        <v>-3.139464904011719</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.88200044499037</v>
+        <v>1.883405613020948</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3841649855248279</v>
+        <v>-0.385232066257481</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.909049007624486</v>
+        <v>2.908408759184894</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.528158215018236</v>
+        <v>-3.524645294941791</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.726470827431204</v>
+        <v>1.727875995461782</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3841649855248279</v>
+        <v>-0.385232066257481</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.90759154643735</v>
+        <v>2.906951297997757</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.871840988244898</v>
+        <v>-3.868328068168454</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.590766841595156</v>
+        <v>1.592172009625733</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4920710375520461</v>
+        <v>-0.4931381182846992</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.844617038675635</v>
+        <v>2.843976790236043</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.229491338483246</v>
+        <v>-4.225978418406802</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.443812760156074</v>
+        <v>1.445217928186652</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8497213877903942</v>
+        <v>-0.8507884685230473</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.626132887188884</v>
+        <v>2.625492638749292</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.538725441479297</v>
+        <v>-4.535212521402853</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.321892045657913</v>
+        <v>1.323297213688491</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8497213877903942</v>
+        <v>-0.8507884685230473</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.627905813889143</v>
+        <v>2.627265565449551</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.970531234629084</v>
+        <v>-4.96701831455264</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.135502615865403</v>
+        <v>1.13690778389598</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9861388842316612</v>
+        <v>-0.9872059649643143</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.532388203491788</v>
+        <v>2.531747955052196</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.205225228761637</v>
+        <v>-5.201712308685193</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.029909793214473</v>
+        <v>1.03131496124505</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.979802617002406</v>
+        <v>-0.9808696977350592</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.524474738831431</v>
+        <v>2.523834490391839</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.540887875992089</v>
+        <v>-5.537374955915645</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8942253259782569</v>
+        <v>0.8956304940088344</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.979802617002406</v>
+        <v>-0.9808696977350592</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.523055330487396</v>
+        <v>2.522415082047805</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.904514120892403</v>
+        <v>-5.901001200815958</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.755262388252373</v>
+        <v>0.7566675562829506</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.078024253869532</v>
+        <v>-1.079091334602185</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.470609908601363</v>
+        <v>2.46996966016177</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.269641503531149</v>
+        <v>-6.266128583454705</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6084659502027057</v>
+        <v>0.6098711182332832</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.374335038168544</v>
+        <v>-1.375402118901198</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.292077953027786</v>
+        <v>2.291437704588194</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.678230280711828</v>
+        <v>-6.674717360635384</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4437919833451929</v>
+        <v>0.4451971513757709</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.782923815349223</v>
+        <v>-1.783990896081876</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.045686230734138</v>
+        <v>2.045045982294546</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.091212764852922</v>
+        <v>-7.087699844776478</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2737844221602161</v>
+        <v>0.2751895901907937</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.782923815349223</v>
+        <v>-1.783990896081876</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.040871663205599</v>
+        <v>2.040231414766007</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.507604639139919</v>
+        <v>-7.504091719063475</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1052217230542944</v>
+        <v>0.106626891084872</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.782923815349223</v>
+        <v>-1.783990896081876</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.038865713814476</v>
+        <v>2.038225465374884</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.884281649669764</v>
+        <v>-7.88076872959332</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.03519039048896433</v>
+        <v>-0.03378522245838678</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.782923815349223</v>
+        <v>-1.783990896081876</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.049124404483155</v>
+        <v>2.048484156043563</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.230156471654572</v>
+        <v>-8.226643551578128</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1774407541371925</v>
+        <v>-0.176035586106615</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.782923815349223</v>
+        <v>-1.783990896081876</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.045223969628851</v>
+        <v>2.044583721189259</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.392298742117665</v>
+        <v>-8.388785822041221</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2438927422674286</v>
+        <v>-0.2424875742368511</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.782923815349223</v>
+        <v>-1.783990896081876</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.043628889683851</v>
+        <v>2.04298864124426</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.688960083927864</v>
+        <v>-8.685447163851419</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3587783030622997</v>
+        <v>-0.3573731350317222</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.851666951083101</v>
+        <v>-1.852734031815755</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.006161984172732</v>
+        <v>2.005521735733141</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.122309192038099</v>
+        <v>-9.118796271961655</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5361442508407972</v>
+        <v>-0.5347390828102192</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.851666951083101</v>
+        <v>-1.852734031815755</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.00213567963833</v>
+        <v>2.001495431198737</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.50531058078073</v>
+        <v>-9.501797660704286</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6894469076594336</v>
+        <v>-0.6880417396288561</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.851666951083101</v>
+        <v>-1.852734031815755</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.002033578316746</v>
+        <v>2.001393329877153</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.662709460993851</v>
+        <v>-9.659196540917407</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7498349437732519</v>
+        <v>-0.7484297757426739</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.009065831296223</v>
+        <v>-2.010132912028876</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.910165766160303</v>
+        <v>1.909525517720711</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.02223978349785</v>
+        <v>-10.01872686342141</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8882967694768018</v>
+        <v>-0.8868916014462247</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.009065831296223</v>
+        <v>-2.010132912028876</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.915516069458353</v>
+        <v>1.914875821018761</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.34863981216287</v>
+        <v>-10.34512689208642</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.01094076098563</v>
+        <v>-1.009535592955052</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.335465859961236</v>
+        <v>-2.336532940693889</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.727592072216523</v>
+        <v>1.726951823776931</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.56778878023706</v>
+        <v>-10.56427586016062</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.09555859759354</v>
+        <v>-1.094153429562962</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.554614828035433</v>
+        <v>-2.555681908768086</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.599144441993773</v>
+        <v>1.598504193554181</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.56409785528065</v>
+        <v>-10.56058493520421</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.094082227610976</v>
+        <v>-1.092677059580398</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.554614828035433</v>
+        <v>-2.555681908768086</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.599144441993773</v>
+        <v>1.598504193554181</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.76835603061052</v>
+        <v>-10.76484311053407</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.170272300624279</v>
+        <v>-1.168867132593701</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.682253772649422</v>
+        <v>-2.683320853382075</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.528074272344022</v>
+        <v>1.52743402390443</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.98639380224169</v>
+        <v>-10.98288088216525</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.253004854792314</v>
+        <v>-1.251599686761736</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.857024540745321</v>
+        <v>-2.858091621477974</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.427694365970919</v>
+        <v>1.427054117531327</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.91292397057424</v>
+        <v>-10.9094110504978</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.208245220631913</v>
+        <v>-1.206840052601335</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.783554709077873</v>
+        <v>-2.784621789810526</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.487147966464809</v>
+        <v>1.486507718025217</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.08804838796079</v>
+        <v>-11.08453546788434</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.263739766839014</v>
+        <v>-1.262334598808436</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.958679126464416</v>
+        <v>-2.95974620719707</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.3966285367804</v>
+        <v>1.395988288340807</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.32250048197528</v>
+        <v>-11.31898756189883</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.364739769346406</v>
+        <v>-1.363334601315828</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.958679126464416</v>
+        <v>-2.95974620719707</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.389409371878804</v>
+        <v>1.388769123439211</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.61030432651252</v>
+        <v>-11.60679140643607</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.486533497935277</v>
+        <v>-1.485128329904699</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.246482971001655</v>
+        <v>-3.247550051734308</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.210054874382485</v>
+        <v>1.209414625942892</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.84012877367634</v>
+        <v>-11.8366158535999</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.577347486962251</v>
+        <v>-1.575942318931673</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.409130508071815</v>
+        <v>-3.410197588804468</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.113582141978945</v>
+        <v>1.112941893539352</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.0721576934126</v>
+        <v>-12.06864477333616</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.667465326227641</v>
+        <v>-1.666060158197064</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.471143205260238</v>
+        <v>-3.472210285992892</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.079068252295005</v>
+        <v>1.078428003855413</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.02014217944379</v>
+        <v>-12.01662925936735</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.642668784953715</v>
+        <v>-1.641263616923137</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.471143205260238</v>
+        <v>-3.472210285992892</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.083058587981406</v>
+        <v>1.082418339541814</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.16181402116791</v>
+        <v>-12.15830110109147</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.700812748542105</v>
+        <v>-1.699407580511527</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.471143205260238</v>
+        <v>-3.472210285992892</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.081583361082664</v>
+        <v>1.080943112643072</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.11222317674308</v>
+        <v>-12.10871025666663</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.665923000607299</v>
+        <v>-1.664517832576721</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.421552360835404</v>
+        <v>-3.422619441568058</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.126391277902437</v>
+        <v>1.125751029462845</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.91307106950598</v>
+        <v>-11.90955814942953</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.599313291359142</v>
+        <v>-1.597908123328564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.256229834885591</v>
+        <v>-3.257296915618245</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.212533659825642</v>
+        <v>1.21189341138605</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.83479371444683</v>
+        <v>-11.68371299671012</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.558423276299276</v>
+        <v>-1.497990989204591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.213672186600902</v>
+        <v>-3.215370240031081</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.247647321832664</v>
+        <v>1.246628489774557</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.54851890212414</v>
+        <v>-11.39743818438743</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.44277420681414</v>
+        <v>-1.382341919719454</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.213672186600902</v>
+        <v>-3.215370240031081</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.248786466388723</v>
+        <v>1.247767634330616</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.60141419016843</v>
+        <v>-11.45033347243171</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.461298547869746</v>
+        <v>-1.400866260775061</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.208716840512456</v>
+        <v>-3.210414893942635</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.254393448203899</v>
+        <v>1.253374616145791</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.31750545923968</v>
+        <v>-11.16642474150296</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.342001351259611</v>
+        <v>-1.281569064164925</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.208716840512456</v>
+        <v>-3.210414893942635</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.260127152442535</v>
+        <v>1.259108320384428</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.20208453510158</v>
+        <v>-11.05100381736487</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.305570243998237</v>
+        <v>-1.245137956903552</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.09329591637436</v>
+        <v>-3.094993969804539</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.319642444531527</v>
+        <v>1.31862361247342</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.93824766789751</v>
+        <v>-10.7871669501608</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.209918978429517</v>
+        <v>-1.149486691334831</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.09329591637436</v>
+        <v>-3.094993969804539</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.30975896321862</v>
+        <v>1.308740131160512</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.67100586702911</v>
+        <v>-10.5199251492924</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.104856818581531</v>
+        <v>-1.044424531486846</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.09329591637436</v>
+        <v>-3.094993969804539</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.307924402719246</v>
+        <v>1.306905570661138</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.54769993855089</v>
+        <v>-10.39661922081418</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.055834762163704</v>
+        <v>-0.9954024750690196</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.003878245246797</v>
+        <v>-3.005576298676976</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.361274690422323</v>
+        <v>1.360255858364215</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.52374639757494</v>
+        <v>-10.37266567983822</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.045584839627828</v>
+        <v>-0.9851525525331426</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.97992470427084</v>
+        <v>-2.981622757701019</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.376315321153391</v>
+        <v>1.375296489095283</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.25968645925214</v>
+        <v>-10.10860574151543</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9532211804604609</v>
+        <v>-0.8927888933657755</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.715864765948043</v>
+        <v>-2.717562819378222</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.521490967985316</v>
+        <v>1.520472135927209</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.552606835747302</v>
+        <v>-9.401526118010588</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6731763647188269</v>
+        <v>-0.612744077624142</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.715864765948043</v>
+        <v>-2.717562819378222</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.518703934325015</v>
+        <v>1.517685102266908</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.512422537381111</v>
+        <v>-9.361341819644398</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6567590214845094</v>
+        <v>-0.5963267343898244</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.675680467581853</v>
+        <v>-2.677378521012031</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.543158137232571</v>
+        <v>1.542139305174464</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.432352741843307</v>
+        <v>-9.281272024106594</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6253642820486309</v>
+        <v>-0.5649319949539455</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.595610672044049</v>
+        <v>-2.597308725474227</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.590566835776011</v>
+        <v>1.589548003717904</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.198871519613707</v>
+        <v>-9.047790801876996</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5240473643189385</v>
+        <v>-0.463615077224254</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.36212944981445</v>
+        <v>-2.363827503244629</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.738579997951622</v>
+        <v>1.737561165893515</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.019162989469834</v>
+        <v>-8.868082271733122</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4550561625743486</v>
+        <v>-0.394623875479664</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.304957945651754</v>
+        <v>-2.306655999081933</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.769990690136281</v>
+        <v>1.768971858078173</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.886887515838946</v>
+        <v>-8.735806798102235</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4067784863749666</v>
+        <v>-0.3463461992802821</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.172682472020868</v>
+        <v>-2.174380525451046</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.844723461061839</v>
+        <v>1.843704629003732</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.696287841165793</v>
+        <v>-8.545207123429082</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3277235558180682</v>
+        <v>-0.2672912687233837</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.982082797347715</v>
+        <v>-1.983780850777894</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.961898326553368</v>
+        <v>1.960879494495261</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.447288042482212</v>
+        <v>-8.296207324745501</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.215217295120977</v>
+        <v>-0.1547850080262925</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.982082797347715</v>
+        <v>-1.983780850777894</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.974804667777026</v>
+        <v>1.973785835718919</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.552878032255316</v>
+        <v>-8.401797314518605</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3854292206294376</v>
+        <v>-0.3249969335347531</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.087672787120819</v>
+        <v>-2.089370840550998</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.783474744313945</v>
+        <v>1.782455912255838</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.571612934373913</v>
+        <v>-8.420532216637202</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.34437883959979</v>
+        <v>-0.2839465525051055</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.087672787120819</v>
+        <v>-2.089370840550998</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.832019086191032</v>
+        <v>1.831000254132924</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.423672892966314</v>
+        <v>-8.272592175229603</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4050817457249178</v>
+        <v>-0.3446494586302333</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.067351871212262</v>
+        <v>-2.069049924642441</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.724332713047999</v>
+        <v>1.723313880989891</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.399444256577342</v>
+        <v>-8.24836353884063</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4041042774228072</v>
+        <v>-0.3436719903281227</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.04312323482329</v>
+        <v>-2.044821288253468</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.730155908627904</v>
+        <v>1.729137076569796</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.35589584980665</v>
+        <v>-8.204815132069939</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3936455268096237</v>
+        <v>-0.3332132397149392</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.04312323482329</v>
+        <v>-2.044821288253468</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.723195296532811</v>
+        <v>1.722176464474703</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.113747456352792</v>
+        <v>-7.962666738616081</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2823238150469374</v>
+        <v>-0.2218915279522529</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.04312323482329</v>
+        <v>-2.044821288253468</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.737657650913954</v>
+        <v>1.736638818855846</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.050518084584445</v>
+        <v>-7.899437366847732</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2624999458804034</v>
+        <v>-0.2020676587857184</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.04312323482329</v>
+        <v>-2.044821288253468</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.732189771373149</v>
+        <v>1.731170939315041</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.927226949767314</v>
+        <v>-7.776146232030602</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2156853979429743</v>
+        <v>-0.1552531108482893</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.919832100006159</v>
+        <v>-1.921530153436338</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.803662546274004</v>
+        <v>1.802643714215896</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.90607775086387</v>
+        <v>-7.754997033127158</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1995247401442715</v>
+        <v>-0.139092453049587</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.898682901102716</v>
+        <v>-1.900380954532895</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.824053043853395</v>
+        <v>1.823034211795288</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.662312308880426</v>
+        <v>-7.511231591143714</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1062378550038434</v>
+        <v>-0.04580556790915846</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.898682901102716</v>
+        <v>-1.900380954532895</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.819833752200446</v>
+        <v>1.818814920142338</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.398284241687167</v>
+        <v>-7.247203523950454</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.001497685793476755</v>
+        <v>0.06192997288816171</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.696817502286762</v>
+        <v>-1.698515555716941</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.943077305410034</v>
+        <v>1.942058473351926</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.148433847738092</v>
+        <v>-6.997353130001379</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.09417991835680839</v>
+        <v>0.1546122054514938</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.696817502286762</v>
+        <v>-1.698515555716941</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.935819380393736</v>
+        <v>1.934800548335629</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.97254175527066</v>
+        <v>-6.821461037533947</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.16813587886443</v>
+        <v>0.2285681659591154</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.696817502286762</v>
+        <v>-1.698515555716941</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.939418503914385</v>
+        <v>1.938399671856277</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.899061846418645</v>
+        <v>-6.747981128681932</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2108553484597899</v>
+        <v>0.2712876355544749</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.623337593434748</v>
+        <v>-1.625035646864927</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.996833955280147</v>
+        <v>1.99581512322204</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.674028846749822</v>
+        <v>-6.522948129013109</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.299889025943616</v>
+        <v>0.3603213130383009</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.398304593765925</v>
+        <v>-1.400002647196104</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.130874232697737</v>
+        <v>2.12985540063963</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.459394469113415</v>
+        <v>-6.308313751376702</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.390437578052496</v>
+        <v>0.450869865147181</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.183670216129519</v>
+        <v>-1.185368269559697</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.264349660333899</v>
+        <v>2.263330828275792</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.192794112139064</v>
+        <v>-6.04171339440235</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4782719796260322</v>
+        <v>0.5387042667207176</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.183670216129519</v>
+        <v>-1.185368269559697</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.245543919117694</v>
+        <v>2.244525087059587</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.952363615334203</v>
+        <v>-5.80128289759749</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5761872549728539</v>
+        <v>0.6366195420675389</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9432397193246582</v>
+        <v>-0.9449377727548369</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.391545293825488</v>
+        <v>2.390526461767381</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.709572807684758</v>
+        <v>-5.558492089948045</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6772328918674524</v>
+        <v>0.7376651789621373</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9432397193246582</v>
+        <v>-0.9449377727548369</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.395474607660308</v>
+        <v>2.394455775602201</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.593632958059573</v>
+        <v>-5.442552240322859</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7242874156348664</v>
+        <v>0.7847197027295514</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8664179883085343</v>
+        <v>-0.868116041738713</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.442246230187322</v>
+        <v>2.441227398129215</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.350977369636409</v>
+        <v>-5.199896651899696</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8183477222241251</v>
+        <v>0.8787800093188105</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8664179883085343</v>
+        <v>-0.868116041738713</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.439244301407316</v>
+        <v>2.438225469349209</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.130956571599398</v>
+        <v>-4.979875853862685</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9079350784495435</v>
+        <v>0.9683673655442289</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7251981432405541</v>
+        <v>-0.7268961966707328</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.525555245458718</v>
+        <v>2.524536413400611</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.931707941694589</v>
+        <v>-4.780627223957876</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.003528713213291</v>
+        <v>1.063961000307976</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7251981432405541</v>
+        <v>-0.7268961966707328</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.541449428260542</v>
+        <v>2.540430596202434</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.772192838175219</v>
+        <v>-4.621112120438506</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.06848059906134</v>
+        <v>1.128912886156026</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5656830397211842</v>
+        <v>-0.5673810931513629</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.638304334812466</v>
+        <v>2.637285502754358</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.627520693075482</v>
+        <v>-4.476439975338769</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.136437559662675</v>
+        <v>1.19686984675736</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4210108946214468</v>
+        <v>-0.4227089480516255</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.735195724433748</v>
+        <v>2.734176892375641</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.687395520433174</v>
+        <v>-4.536314802696461</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.098525120121024</v>
+        <v>1.158957407215709</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4808857219791389</v>
+        <v>-0.4825837754093176</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.685308319420558</v>
+        <v>2.684289487362451</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.600596022654166</v>
+        <v>-4.449515304917453</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.155645412555194</v>
+        <v>1.216077699649879</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4808857219791389</v>
+        <v>-0.4825837754093176</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.707708812743125</v>
+        <v>2.706689980685017</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.603065729115972</v>
+        <v>-4.451985011379259</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.154729931343883</v>
+        <v>1.215162218438568</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.483355428440945</v>
+        <v>-0.4850534818711237</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.706299390239453</v>
+        <v>2.705280558181346</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.671435915439982</v>
+        <v>-4.520355197703269</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.138388779288981</v>
+        <v>1.198821066383666</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4740797294047301</v>
+        <v>-0.4757777828349088</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.722871732135884</v>
+        <v>2.721852900077776</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.550019485813506</v>
+        <v>-4.398938768076793</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.177392059771463</v>
+        <v>1.237824346866148</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4740797294047301</v>
+        <v>-0.4757777828349088</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.713308440767775</v>
+        <v>2.712289608709668</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.581012645142211</v>
+        <v>-4.429931927405498</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9897043610803677</v>
+        <v>1.050136648175053</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4740797294047301</v>
+        <v>-0.4757777828349088</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.538018005808162</v>
+        <v>2.536999173750055</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.405538385349741</v>
+        <v>-4.254457667613028</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.064461296989143</v>
+        <v>1.124893584083829</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4740797294047301</v>
+        <v>-0.4757777828349088</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.54258523779995</v>
+        <v>2.541566405741842</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.51647463799099</v>
+        <v>-4.365393920254277</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.020098269819441</v>
+        <v>1.080530556914127</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4740797294047301</v>
+        <v>-0.4757777828349088</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.542596711686747</v>
+        <v>2.54157787962864</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.719501215534224</v>
+        <v>-4.56842049779751</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9420190240220536</v>
+        <v>1.002451311116739</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6771063069479635</v>
+        <v>-0.6788043603781422</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.423912150380713</v>
+        <v>2.422893318322606</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.561575616598931</v>
+        <v>-4.410494898862217</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.015361650028303</v>
+        <v>1.075793937122989</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6771063069479635</v>
+        <v>-0.6788043603781422</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.434084536812845</v>
+        <v>2.433065704754738</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.709896870410059</v>
+        <v>-4.558816152673346</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9509794190777121</v>
+        <v>1.011411706172397</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6771063069479635</v>
+        <v>-0.6788043603781422</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.429030807386706</v>
+        <v>2.428011975328598</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.71107995506112</v>
+        <v>-4.559999237324407</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9422819606618134</v>
+        <v>1.002714247756499</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.682749355414475</v>
+        <v>-0.6844474088446537</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.417420753751324</v>
+        <v>2.416401921693217</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.587952248067037</v>
+        <v>-4.436871530330324</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9920849164925483</v>
+        <v>1.052517203587233</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.682749355414475</v>
+        <v>-0.6844474088446537</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.417972626784425</v>
+        <v>2.416953794726318</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.495141766616177</v>
+        <v>-4.344061048879464</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9584818009642577</v>
+        <v>1.018914088058943</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5899388739636157</v>
+        <v>-0.5916369273937944</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.402931607546307</v>
+        <v>2.4019127754882</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.446578714395147</v>
+        <v>-4.295497996658434</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9797804977772704</v>
+        <v>1.040212784871956</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5413758217425855</v>
+        <v>-0.5430738751727642</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.433942914803526</v>
+        <v>2.432924082745419</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.333907496158897</v>
+        <v>-4.182826778422184</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.019924693583494</v>
+        <v>1.080356980678179</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4287046035063353</v>
+        <v>-0.430402656936514</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.496621354256999</v>
+        <v>2.495602522198892</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.221530494976224</v>
+        <v>-4.070449777239511</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.07036678988723</v>
+        <v>1.130799076981915</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4287046035063353</v>
+        <v>-0.430402656936514</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.502112650087666</v>
+        <v>2.501093818029559</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.419765063862955</v>
+        <v>-4.268684346126242</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.002570164101077</v>
+        <v>1.063002451195762</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6269391723930658</v>
+        <v>-0.6286372258232445</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.394669110524167</v>
+        <v>2.39365027846606</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.502766344888234</v>
+        <v>-4.351685627151521</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8077253716916184</v>
+        <v>0.8681576587863036</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6455100569202397</v>
+        <v>-0.6472081103504184</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.221882299808516</v>
+        <v>2.220863467750409</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,13 +46447,13 @@
         <v>2.821532688588707</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.502766344888234</v>
+        <v>-4.351685627151521</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8077253716916184</v>
+        <v>0.8681576587863036</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6455100569202397</v>
+        <v>-0.6472081103504184</v>
       </c>
       <c r="G1952" t="n">
         <v>2.814596485575075</v>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,37 +824,37 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-50.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.7%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.9%</t>
+          <t>134.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.7%</t>
+          <t>-55.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.7%</t>
+          <t>-617.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-43.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-289.4%</t>
+          <t>-297.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>-223.7%</t>
         </is>
       </c>
     </row>
@@ -46444,19 +46444,19 @@
         <v>3.883950904316143</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.821532688588707</v>
+        <v>2.61118425402852</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.351685627151521</v>
+        <v>-4.558697542656448</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8681576587863036</v>
+        <v>0.7873488126521933</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.6472081103504184</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.814596485575075</v>
+        <v>2.222859387818269</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240502.xlsx
+++ b/tame_output/ON/bt/strategyON_20240502.xlsx
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353075</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544784</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -46447,10 +46447,10 @@
         <v>2.61118425402852</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.558697542656448</v>
+        <v>-4.558656227338767</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7873488126521933</v>
+        <v>0.7873653387792658</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.6472081103504184</v>
